--- a/GearSage-client/pkgGear/data_raw/keitech_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/keitech_lure_import.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:O34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,6 +445,9 @@
       <c r="N1" t="str">
         <v>description</v>
       </c>
+      <c r="O1" t="str">
+        <v>official_link</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -466,28 +469,31 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H2" t="str">
         <v>soft</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202501241430404411.jpg</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>スイムベイトの名作を、忠実に、完全復刻！ 野尻湖や桧原湖をはじめとするハイランドクリアレイクのシークレットとして噂がうわさを呼び、ローカルの猛者たちから一般アングラーへと徐々に浸透、やがて定番化したTEMPTブランドの『スイングベイト』。 惜しまれながらも廃盤となったこのスイムベイト（シャッドテールワーム）を、ケイテックが完全復刻いたしました。</v>
+      </c>
+      <c r="O2" t="str">
+        <v>https://keitech.co.jp/pages/613/</v>
       </c>
     </row>
     <row r="3">
@@ -510,28 +516,31 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H3" t="str">
         <v>soft</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191540483278.jpg</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>キビキビと、そして大きくスイングするテールアクション。ボトムでのズル引きやカーブフォールによるスイミングで効果絶大です。水を良く掴み、水流負けしないテールデザインがミソ。ジグヘッドはもとより、テキサス、キャロライナ、ダウンショットリグ、そしてネコリグやジグトレーラー等、あらゆる使い方で効果を発揮します。あまりシェイク等の小技を入れずに、スローにシンプルに使うことをお勧めいたします。</v>
+      </c>
+      <c r="O3" t="str">
+        <v>https://keitech.co.jp/pages/39/</v>
       </c>
     </row>
     <row r="4">
@@ -554,28 +563,31 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H4" t="str">
         <v>soft</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191547352876.jpg</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>ワイドなスイングアクション、最強の水噛み、絶妙なロール、群を抜く集魚力。ある時はアシを抜けるスピナーベイト、ある時はボトムをつつくクランクベイト、ある時はウィードに絡むテキサスリグワーム、ある時は優秀なジグトレーラー…。試行錯誤の末に行きついた究極の広域性能をありったけの技術でお届け致します。</v>
+      </c>
+      <c r="O4" t="str">
+        <v>https://keitech.co.jp/pages/57/</v>
       </c>
     </row>
     <row r="5">
@@ -598,28 +610,31 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>swimbait</v>
       </c>
       <c r="H5" t="str">
         <v>soft</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>wobble_roll</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191558078979.jpg</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>機敏なテールアクション、完璧なバランス、そして絶妙なロール･･･。確かに、そしてイージーに釣果を伸ばすための特別なスペックです。ただ巻くだけで反応してしまう。そんな魚のいかに多いことか、をご自信でお確かめ下さい。イージーシャイナー、好評発売中。</v>
+      </c>
+      <c r="O5" t="str">
+        <v>https://keitech.co.jp/pages/232/</v>
       </c>
     </row>
     <row r="6">
@@ -642,28 +657,31 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H6" t="str">
         <v>soft</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161646502833.jpg</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:33.792Z</v>
       </c>
       <c r="M6" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:33.792Z</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>これが、ケイテックのバックスライド“専用”ワームバックスライド仕様の高比重ワームが釣れる理由のひとつに、文字どおり後方へのスライドフォールが挙げられます。同じカバー攻略でも、それはジグやテキサスリグにはけっして真似のできない芸当。いや、数多あるなかで、アングラーから逆の方向へと慣性が働くルアー自体、たぐいまれ。だから『グライドカマロン』の開発は、“いかにバックスライドさせるか”に重きを置きました。魚にこたえを聞いた理想的なフォール姿勢とスライド幅は、ハサミやヒゲを含めたボディデザインとマテリアルのたまもの。もちろん、フォール後のボトムステイやロッドワークでアクションを与えた際の挙動、カバーの抜け方（抜きやすさ）、回収のしやすさも徹底的に検証しています。オープンウォーターのミドストやボトストなど、自由な発想で使い方の幅を拡げていくのは釣りの醍醐味ですが、まずはノーシンカーリグでの、バックスライドを活かしたシャローカバー攻略を強くおすすめいたします。</v>
+      </c>
+      <c r="O6" t="str">
+        <v>https://keitech.co.jp/pages/608/</v>
       </c>
     </row>
     <row r="7">
@@ -686,28 +704,31 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H7" t="str">
         <v>soft</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161654221750.jpg</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:35.679Z</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:35.679Z</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>それまで、 障害物周りやボトムでのスローな誘いに限定されていたワームフィッシングに、表・中層で巻いて喰わせるという革命的ストラテジーの扉を開いたカーリーテールグラブ。バスアングラーが増加の一途をたどった90年代中盤、投げて巻くだけのシンプルな操作で魚を手にすることのできるこのルアーは、バス釣りそのものの門戸を広げる重要な役割を担っていました。 『フラッパーグラブ』はまさにこの“投げて巻く”というシンプルな使用法に重きを置いて開発。したがって適するリグはさまざまあれど、私たちがもっともおすすめしたいのはずばり、ノーシンカーリグでのグラビンバズです。水面を使い、食性だけでなくリアクション的要素でもバスを反応させる釣法はむしろいまの時勢に即しており、一連の動作をよどみなく続けるための理想を形にしています。 釣法が細分化され、高度な技術を要する場面も少なくない昨今にあって、シンプルに、投げて巻いて、巻いて投げて、ルアー釣りの醍醐味を味わうためのツール、それが『フラッパーグラブ』なのです。</v>
+      </c>
+      <c r="O7" t="str">
+        <v>https://keitech.co.jp/pages/599/</v>
       </c>
     </row>
     <row r="8">
@@ -730,28 +751,31 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H8" t="str">
         <v>soft</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191655435515.jpg</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:37.181Z</v>
       </c>
       <c r="M8" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:37.181Z</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>まだシリコンスカート仕様の“スモラバ”が存在していなかったころに発売を開始、以来、釣れるワームとしての位置付けをゆるぎないものとしてきた『リトルスパイダー』。そのたしかなコンセプトを継承しつつ、個体数減少が叫ばれる昨今のフィールド事情に最適化したもうひとつのフィネススカーテッドベイトこそ『ハイパースパイダー』です。『リトルスパイダー』との最大の相違点は、アクション入力時の存在感にあります。水のつかみ方、押し方、逃がし方を徹底的に検証し、全パーツをイチから設計。フォール、スイミング、シェイク…リグに合わせたどんな誘い方でも各部がレスポンスよく強く作動し、そのサイズからは想像できない誘引力を発揮します。『リトルスパイダー』との併用で根こそぎ釣るもよし、一発狙いの切り札として起用するもよし、強さを備えたフィネスの新たなトビラを開いてください。</v>
+      </c>
+      <c r="O8" t="str">
+        <v>https://keitech.co.jp/pages/582/</v>
       </c>
     </row>
     <row r="9">
@@ -774,28 +798,31 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H9" t="str">
         <v>soft</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191701313136.jpg</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:39.295Z</v>
       </c>
       <c r="M9" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:39.295Z</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>カバーゲームをアップデートする、 第三世代パドルテールグラブ『パドリンビーバー』。アプローチがスムーズに行なえること。しっかりとバスを誘えること。あらゆる障害物で使用できること。これらは、ともするとキャスト数が釣果に直結する現代のカバーフィッシングにおいて、とても大切な要素だと言えるでしょう。さらに効率を高めたい。そんなカバーフィッシャーマンの“釣欲”を満たすべく、熟慮と実践を繰り返して辿り着いた形状こそがパドルテールグラブでした。 『パドリンビーバー』。カバーゲームをアップデートするための、我々からの提案です。</v>
+      </c>
+      <c r="O9" t="str">
+        <v>https://keitech.co.jp/pages/581/</v>
       </c>
     </row>
     <row r="10">
@@ -818,28 +845,31 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H10" t="str">
         <v>soft</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20250418163325698.jpg</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:40.991Z</v>
       </c>
       <c r="M10" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:40.991Z</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>エビ食いバスを刺激する、エビ系クローラー。エビを捕食するバスを釣るために開発したエビ系クローラー『ネコカマロン』。特にネコリグでの使用において、入水姿勢、着底後の倒れ込み、シェイク時のボディ部横振りアクションなど、着水からピックアップまで、水中にいる間、常に“エビ食いバス”を刺激するよう各パーツをデザインしました。素材は硬すぎず、柔らかすぎずの中弾性材料に、エビの淡い存在感を再現するための適量な塩、そして釣れる匂いと評判の“天然イカフレーバー”を配合しました。</v>
+      </c>
+      <c r="O10" t="str">
+        <v>https://keitech.co.jp/pages/551/</v>
       </c>
     </row>
     <row r="11">
@@ -862,28 +892,31 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H11" t="str">
         <v>soft</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191729594683.jpg</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:42.698Z</v>
       </c>
       <c r="M11" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:42.698Z</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>長年にわたり、ジグフィッシャーマンがこだわったジグ着底時の自発的アクションがあります。ジグ着底後“パッ”とスカートがフレアし、少し遅れて“テローン”とトレーラーが倒れこむ。テロテロ１軍ポークでのみ出し得たこの“余韻アクション”は今までに多くのバスを虜にしてきました。そのなまめかしい動きを再現すべく開発したプラスティックチャンクこそが“フレックスチャンク”です。肉厚な脚をフレキシブルにアクションさせる“マクラギ構造”。最適な材料の柔らかさ、塩含有量による最適な比重。バイトを強烈に誘発する“天然イカフレーバー”。そしてワーム素材ならではの自在なカラーリング。水押し系チャンクトレーラー、フレックスチャンクの完成です。</v>
+      </c>
+      <c r="O11" t="str">
+        <v>https://keitech.co.jp/pages/456/</v>
       </c>
     </row>
     <row r="12">
@@ -906,28 +939,31 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H12" t="str">
         <v>soft</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011701561170.jpg</v>
       </c>
       <c r="L12" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:45.196Z</v>
       </c>
       <c r="M12" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:45.196Z</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>コアは細身ながらリングをまとうことで、シルエットにボリュームを持たせつつ生命体ならではの自然な動き＝“Ultimate Lifelike Action”を実現した『イージーシェイカー』。 リングボディ＋ノンソルティマテリアルの組み合わせにより、ジグヘッドリグのスイミング時、あるいはダウンショットリグでボトムから浮かせた状態で誘った時など、絶妙な姿勢に加えて、トリッキーなダートやもだえるような艶めかしいアクションがその名のとおり“イージー”に演出可能となっています。 近年はバスフィッシングのみならず、アジングやロックフィッシュゲームをはじめソルトウォーターの世界でもその効能が認められており、弊社ラインナップのなかにあって「釣れるルアーは魚種を選ばない」を地で行く製品のひとつ。 バスで言うところのウルトラフィネスからオーソドックスなライトリグ仕様まで、ラインナップを拡充してまいりました。フィールドコンディションや対象魚にあわせた、最適なサイズをお選びください。</v>
+      </c>
+      <c r="O12" t="str">
+        <v>https://keitech.co.jp/pages/549/</v>
       </c>
     </row>
     <row r="13">
@@ -950,28 +986,31 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H13" t="str">
         <v>soft</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191804546996.jpg</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:48.055Z</v>
       </c>
       <c r="M13" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:48.055Z</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>チョン掛け専用ダウンショットワーム、究極の食わせ系として名を馳せたカスタムリーチ。私達は、10数年ぶりにこれを復活させることに致しました。とは言っても、当時のままの仕様でのリバイバルではありません。デザイン、製法、そしてパッケージングとそれぞれ意匠を凝らし再開発。今の私達をして、「最高の仕事」と言えるレベルにまで高めての復活です。</v>
+      </c>
+      <c r="O13" t="str">
+        <v>https://keitech.co.jp/pages/450/</v>
       </c>
     </row>
     <row r="14">
@@ -994,28 +1033,31 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H14" t="str">
         <v>soft</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011702381439.jpg</v>
       </c>
       <c r="L14" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:51.253Z</v>
       </c>
       <c r="M14" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:51.253Z</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>水面をキープしながらスロー＆ステディなリトリーブ。微かなスプラッシュと均質な引き波を水面に作り込む。ノイジーフラッパーの大いなるバス吸引力は、こうした静かな展開でこそ発揮されます。カバーにタイトに、ゆっくり滑らかに、期待を膨らませて･･･。魔性のバジングフロッグ、ノイジーフラッパー。</v>
+      </c>
+      <c r="O14" t="str">
+        <v>https://keitech.co.jp/pages/423/</v>
       </c>
     </row>
     <row r="15">
@@ -1038,28 +1080,31 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H15" t="str">
         <v>soft</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191814411193.jpg</v>
       </c>
       <c r="L15" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:55.263Z</v>
       </c>
       <c r="M15" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:55.263Z</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>あまたあるザリガニワームの中で輝くような異彩を放つ。超アクション系クローワーム、クレイジーフラッパー!!</v>
+      </c>
+      <c r="O15" t="str">
+        <v>https://keitech.co.jp/pages/381/</v>
       </c>
     </row>
     <row r="16">
@@ -1082,28 +1127,31 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H16" t="str">
         <v>soft</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191820097952.jpg</v>
       </c>
       <c r="L16" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:40:06.614Z</v>
       </c>
       <c r="M16" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:40:06.614Z</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>ライフライクな動きを追求したピンテール系ストレートワーム。ワームに与えられた全ての動きは、完成されたテーパーデザインにより横振りテールアクションに変換。本物のベイトフィッシュに見まごうばかりのリアルさです。ノーシンカーのただ巻きから、ジグヘッド、ダウンショット、果てはヘビーテキサスまであらゆるリグにフィット。2.8”〜5.8”すべてワームをクセから守る専用ブリスターケースにてお届けします。もちろん強力天然イカフレーバー配合。バイトを長く、そして深くします。</v>
+      </c>
+      <c r="O16" t="str">
+        <v>https://keitech.co.jp/pages/158/</v>
       </c>
     </row>
     <row r="17">
@@ -1126,28 +1174,31 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H17" t="str">
         <v>soft</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191828058722.jpg</v>
       </c>
       <c r="L17" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:40:13.153Z</v>
       </c>
       <c r="M17" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:40:13.153Z</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>透明感のある繊細なスカート、そしてピリピリと俊敏に動くダブルテール。シリコンスカート製のスモールラバージグがまだ世に出回っていなかった時代に、林圭一が思い描き開発したフィネススカーテッドグラブです。 当時からジグヘッド、ダウンショット、キャロライナそしてスプリットショットとあらゆるフィネスリグに対応し、常にステディな釣果をマークしてきました。最近のものは、透明感をさらに高めたノンソルティのワーム素材を使用。また天然イカフレーバーを配合した匂いつきの現代仕様でお届けします。 リトルスパイダー。今なおケイテックが誇るフィネスベイトの決定版です。</v>
+      </c>
+      <c r="O17" t="str">
+        <v>https://keitech.co.jp/pages/455/</v>
       </c>
     </row>
     <row r="18">
@@ -1170,28 +1221,31 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H18" t="str">
         <v>soft</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20221219183446307.jpg</v>
       </c>
       <c r="L18" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:40:20.195Z</v>
       </c>
       <c r="M18" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:40:20.195Z</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>ジグヘッドやダウンショット。シェイクすることによりタイトでキレのあるローリングアクションを生み出します。 独自に開発した精密２色成型にこのアクションが相まって超リアルな小魚を表現します。バスはためらいもなく腹からスパッと吸い込んでしまう、そんな強い”食わせ力”を持ったアイテムです。</v>
+      </c>
+      <c r="O18" t="str">
+        <v>https://keitech.co.jp/pages/35/</v>
       </c>
     </row>
     <row r="19">
@@ -1214,28 +1268,31 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H19" t="str">
         <v>soft</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191843366790.jpg</v>
       </c>
       <c r="L19" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:40:24.698Z</v>
       </c>
       <c r="M19" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:40:24.698Z</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>私共が手にした新技術、それは超高精度コアショット成型技術。この新たな技術領域で今までにない機能を持ったワームを作りたい、そんな思いを具現化したのがソルティ・コアチューブ。テキサスリグによるカバー撃ち、ノーシンカー・リバースセットによるバックスライディングと様々なカバーフィッシングに対応。使いやすさと着実な釣果を約束するワームの新ジャンルです。</v>
+      </c>
+      <c r="O19" t="str">
+        <v>https://keitech.co.jp/pages/293/</v>
       </c>
     </row>
     <row r="20">
@@ -1258,28 +1315,31 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H20" t="str">
         <v>soft</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20221219174541338.jpg</v>
       </c>
       <c r="L20" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:40:28.288Z</v>
       </c>
       <c r="M20" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:40:28.288Z</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>デザイン極めたロングカーリーテール。 ウィードエリアでテキサスリグをスイムさせる。琵琶湖に代表されるそんな釣りを視野に開発。ごくスローなリトリーブでも強くワイドに水を掻くよう、特別なテールをデザインしました。ボディ形状にもこだわり、ウィードに対する絶対的な“スナッグレス性能”を盛り込んでいます。マッドワグ。ウィードの隙間をなめらかにかいくぐり、絶え間なく発散される強烈な集魚力。テールとボディのバランスに配慮したうえで４つのサイズそれぞれをしっかりと試し、丹念に作り込んだスイミングテキサス（マキマキ）用ワームの決定版です。</v>
+      </c>
+      <c r="O20" t="str">
+        <v>https://keitech.co.jp/pages/276/</v>
       </c>
     </row>
     <row r="21">
@@ -1302,28 +1362,31 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>worm</v>
       </c>
       <c r="H21" t="str">
         <v>soft</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>variable</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202212191850068911.jpg</v>
       </c>
       <c r="L21" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
+        <v>2026-04-10T05:40:33.878Z</v>
       </c>
       <c r="M21" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
+        <v>2026-04-10T05:40:33.878Z</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>しなやかさと、ぎこちなさが入り混じった本物の生命感。ライブインパクトはそんな温もりを封じ込めたケイテックの会心作。高い汎用性を誇り、どんなリグで 使っても命が宿ったかのようにアクションします。ジグヘッド、ダウンショット、テキサスリグ、ワッキー系リグ、ジグトレーラーとあらゆる用途に対応しま す。 ※ ジグヘッドがボトムで立つほどの高浮力材料を使用。フォールスピードを抑え、ボトムで立つ、あるいは水中で漂う。 ※ 浮力により、ボトムでの根掛かりが激減。 ※ 水噛みに優れたリングボディとナチュラルさを醸し出すフィンテール。※ 歴然とした食いの良さ、天然イカフレーバー配合。</v>
+      </c>
+      <c r="O21" t="str">
+        <v>https://keitech.co.jp/pages/18/</v>
       </c>
     </row>
     <row r="22">
@@ -1346,28 +1409,31 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>spinnerbait</v>
       </c>
       <c r="H22" t="str">
         <v>wire</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>spin_flash</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/20260128162612996.jpg</v>
       </c>
       <c r="L22" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="M22" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>同じワイヤーベイトでも、バズベイトがスピナーベイトと明らかに異なるのはトレースレンジが限定されていること。 投げて、水面を巻く。 この実に単純な作業が、バズベイトを扱うアングラーに与えられた仕事なのです。 もちろん、障害物との距離感等バスのポジションを想定したコース取りは重要だし、状況に応じたスピードコントロールも大切です。</v>
+      </c>
+      <c r="O22" t="str">
+        <v>https://keitech.co.jp/pages/660/</v>
       </c>
     </row>
     <row r="23">
@@ -1390,28 +1456,31 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>spinnerbait</v>
       </c>
       <c r="H23" t="str">
         <v>wire</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>spin_flash</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202501241436271305.jpg</v>
       </c>
       <c r="L23" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="M23" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>日本基準のザ・スピナーベイト『ベイビーTEE-BONEスピナーベイト』オリジナルのTEEボーンスピナーベイトは、奇をてらうことなく、サーチベイトに求められる基本性能「よく飛び、よく動き、よく掛かる」を重視してパーツを選び、デザインに落とし込んだ“ザ・スピナーベイト”。そのコンセプトはまったく変えず、構成要素それぞれの役割をしっかりと調整してコンパクトにまとめたのが『ベイビーTEEボーンスピナーベイト』です。ハイプレッシャーや過度のアピールを嫌う状況において“小さい”ことがバイトチャンス増につながるのは真理であり、その点において日本基準と言えるでしょう。</v>
+      </c>
+      <c r="O23" t="str">
+        <v>https://keitech.co.jp/pages/617/</v>
       </c>
     </row>
     <row r="24">
@@ -1434,28 +1503,31 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>spinnerbait</v>
       </c>
       <c r="H24" t="str">
         <v>wire</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>Variable</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>spin_flash</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202403141759512800.jpg</v>
       </c>
       <c r="L24" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="M24" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>基本性能を、丁寧に紡いだ “Theケイテックカスタム”。誕生してから１世紀が経つとも言われるトラディショナルバスルアー、スピナーベイト。このルアーの特筆すべき基本性能は、ずばり“ウィードレスなサーチベイト”であること。その基本性能にフォーカスをあて、開発いたしました。よく飛び、よく動き、よく掛かる、サーチベイトに重要なこの３つの基本性能を重視しデザイン、部材選定を行ないました。スタンダードスピナーベイトとして、KEITECHが自信をもってお勧めいたします。</v>
+      </c>
+      <c r="O24" t="str">
+        <v>https://keitech.co.jp/pages/554/</v>
       </c>
     </row>
     <row r="25">
@@ -1478,28 +1550,31 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H25" t="str">
         <v>jig</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202407031757493567.jpg</v>
       </c>
       <c r="L25" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="M25" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>ブレーデッドジグという難題へのこたえ『ランブレードジグ』開発の発端は、ケイテックU.S.A.からの提案でした。「スイングインパクトFATをはじめ、多くのアングラーがブレーデッドジグのトレーラーとしてうちのワームを使っている。だから、それに見合ったオリジナルを作ってくれないか？」。バスルアーのカテゴリーのひとつとして定着し、すでに20年。最後発である以上、独自の発想をデザインに落とし込まなければ意味がありません。何より、釣れる道具であることが大前提であるのは、ほかのルアーと同じ。着手から5年。これがブレーデッドジグという難題への、わたしたちのこたえなのです。</v>
+      </c>
+      <c r="O25" t="str">
+        <v>https://keitech.co.jp/pages/625/</v>
       </c>
     </row>
     <row r="26">
@@ -1522,28 +1597,31 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H26" t="str">
         <v>jig</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011732559977.jpg</v>
       </c>
       <c r="L26" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="M26" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>ザ・スタンダード！使う場所・状況を選ばないセミフルサイズジグ多くのアングラーに愛され続けてきたラバージグ・モデルⅠのヘッドデザインを踏襲し、使いやすさを追求しました。モデルⅠと同じ角度で設計した横向きアイ、最適な硬さ・本数・長さでそろえたブラシガードと相まって、障害物に対する適度な引っ掛かり感とその後の絶妙な抜け感はジグマンの要求を高い次元で満たし、ストレスのないカバー攻略を実現可能にします。</v>
+      </c>
+      <c r="O26" t="str">
+        <v>https://keitech.co.jp/pages/575/</v>
       </c>
     </row>
     <row r="27">
@@ -1566,28 +1644,31 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H27" t="str">
         <v>jig</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202601091020542528.jpg</v>
       </c>
       <c r="L27" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="M27" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="N27" t="str">
-        <v/>
+        <v>ラインアイがフックと異なる線径であることにお気づきでしょうか。実はコレ、ヘッドのノーズをよりシャープにしてベジテーションのすり抜け性能を向上させるため、フックとは異なるパーツで構成しているのです。また、アイはラインの結び目がヘッドとの付け根に偏らないよう、オーバル形にデザインしました。</v>
+      </c>
+      <c r="O27" t="str">
+        <v>https://keitech.co.jp/pages/655/</v>
       </c>
     </row>
     <row r="28">
@@ -1610,28 +1691,31 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H28" t="str">
         <v>jig</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011733324565.jpg</v>
       </c>
       <c r="L28" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="M28" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>ボトムノックで食わせる、NEWコンセプトラバージグスカートベイトを得意とするケイテックの新提案。フットボールジグとスイムジグの釣れる要素を抽出し、ハードボトムをスローに巻くだけで甲殻類など底生動物のライブリーなアクションを演出できます。使い方の基本は、ボトムを感じながらゆっくり巻くこと。同じクランキンでも、クランクベイトのボトムノックとは一線を画す、クランキンフットボールジグならではの無二のメソッドをお試しください。</v>
+      </c>
+      <c r="O28" t="str">
+        <v>https://keitech.co.jp/pages/576/</v>
       </c>
     </row>
     <row r="29">
@@ -1654,28 +1738,31 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H29" t="str">
         <v>jig</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161640403055.jpg</v>
       </c>
       <c r="L29" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="M29" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>ボリュームを抑えたコンパクトな仕様。すり抜け性とスナッグレス性を両立するブラシガードホールの構造。トレーラーとマッチするスカートカラーのバリエーション。フレアに優れたシリコンラバーの採用… いまでは当たり前となったジャパニーズジグのさまざまな工夫を、創業当初から独自の発想で盛り込み、必要に応じて都度マイナーチェンジを繰り返してまいりました。 『ModelⅠ』はいわば、ケイテックの理念『経験は、品質に。』を象徴する製品。 四半世紀にわたり愛され続けている理由がそこにあります。そして2023年春、ヘッドの仕様を見直した『モデル Ⅰ Ver.2.0』を、満を持してJIG MANの皆さまにお届けいたします。</v>
+      </c>
+      <c r="O29" t="str">
+        <v>https://keitech.co.jp/pages/602/</v>
       </c>
     </row>
     <row r="30">
@@ -1698,28 +1785,31 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H30" t="str">
         <v>jig</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202401161641262646.jpg</v>
       </c>
       <c r="L30" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="M30" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>カバージグの理想形である『ModelⅠ』のコンセプトやデザインをすべて継承し、このカテゴリーのルアーに本来備わっているビッグフィッシュへの対応力を強化しました。 ヘビーウェイト＆フルサイズでありながら、樹脂タングステンをヘッド素材に用いることで全体ボリュームを抑え高いすり抜け性を発揮。なおかつ、抵抗の大きいバルキートレーラーと組み合わせても力負けすることなく、ヘッドを支点とするメリハリの利いた操作を可能にしています。 つまり、シャローのみならずミドル～ディープボトムのヘビーカバーでもスカーテッドベイトならではの有機的存在感で誘えるわけです。 リーズ帯の奥の奥、折り重なった流木や浮葉植物のヘビーマット、崩落跡のディープウォーターカバーなど、複雑に入り組んだピンスポットさえ狙い撃つことができる、オールレンジ対応“食わせのビッグベイト”。 ボリュームのあるトレーラーと『モデルⅣ』のコンボをそんなイメージでお使いいただくと、ジグフィッシングの新たなトビラが開くはずです。</v>
+      </c>
+      <c r="O30" t="str">
+        <v>https://keitech.co.jp/pages/603/</v>
       </c>
     </row>
     <row r="31">
@@ -1742,28 +1832,31 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H31" t="str">
         <v>jig</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202501300927538741.jpg</v>
       </c>
       <c r="L31" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="M31" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>比重13、樹脂タングステンヘッドのフットボールラバージグ。着底姿勢にこだわりたいミドル～ディープレンジの釣りにうってつけです。 ヘッド素材はとても硬く、鉛製品に比べ感度が大幅にアップ。着底の瞬間やボトムの様子が一層明確に把握できます。繊細なガードは見た目以上の効果。臆することなく水中のストラクチャーを直撃できます。繊細でよくフレアーするオリジナルシリコンスカートSR-40。丁寧かつ熟練の手巻きです。</v>
+      </c>
+      <c r="O31" t="str">
+        <v>https://keitech.co.jp/pages/10/</v>
       </c>
     </row>
     <row r="32">
@@ -1786,28 +1879,31 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H32" t="str">
         <v>jig</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202209221617177492.jpg</v>
       </c>
       <c r="L32" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="M32" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>コンパクトな樹脂タングステン製バナナヘッド、特製スカートを巻いたスクリューパーツ、丈夫な特注フック。ありそうで無かった理想のバランスを手に入れるため、吟味され尽くしたカスタムパーツ達。水面直下や中層をリトリーブする、ボトムをウィードや岩に当てながら泳がせる。従来のラバージグとはまったく違う、新たな境地・機能を開発しました。トレーラーには、弊社『スイングインパクトFAT4.8”』を“強く強く”お勧めいたします。比類なきバランス、バルキーな存在感、強い波動、卓越したウィードレス／スリ抜け性能。ビッグフィッシュを仕留めるための数々の要諦が、この組み合わせには込められています。</v>
+      </c>
+      <c r="O32" t="str">
+        <v>https://keitech.co.jp/pages/206/</v>
       </c>
     </row>
     <row r="33">
@@ -1830,28 +1926,31 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H33" t="str">
         <v>jig</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011735477115.jpg</v>
       </c>
       <c r="L33" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="M33" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="N33" t="str">
-        <v/>
+        <v>比重13樹脂タングステンを用い、カチッとコンパクトに仕上げたガード付きスモールラバージグ。小さいのにしっかりしたガード力、そして軽いくせに目を見張るカバー突破力。繊細かつ大胆にスモールベイトでカバーを攻める、そんな昨今の釣りにマッチしたアイテムです。やや硬め、機敏にフレアーするSR-40シリコンスカートを丁寧に手巻きしています。-0-0-0-0-0-0</v>
+      </c>
+      <c r="O33" t="str">
+        <v>https://keitech.co.jp/pages/13/</v>
       </c>
     </row>
     <row r="34">
@@ -1874,40 +1973,43 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>rubber_jig</v>
       </c>
       <c r="H34" t="str">
         <v>jig</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Bottom</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>flutter_fall</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>pkgGear/images/lure/KEITECH/202208011736112779.jpg</v>
       </c>
       <c r="L34" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="M34" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="N34" t="str">
-        <v/>
+        <v>ラウンドヘッドに今どきのラバーカッティング。そして繊細・精密を極めた“モノ（1本）ガード”。パラアシ、岩、ロープ、ウィード等ほとんどの障害物を難なくクリア、そしてフッキングは超イージーなノーガード感覚に仕上げています。昨今のパワーフィネスを知り尽くした仕様です。デコイ・リマリック #3フック、1/32, 1/20, 1/16, 3/32oz。ヘッドはもちろん比重13、樹脂タングステン製。</v>
+      </c>
+      <c r="O34" t="str">
+        <v>https://keitech.co.jp/pages/14/</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R71"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1973,16 +2075,16 @@
         <v>KL1000</v>
       </c>
       <c r="C2" t="str">
-        <v>スイングベイト2.8"</v>
+        <v>ジグヘッドリグ</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>1/32oz</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>ジグヘッドリグ</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -1991,10 +2093,10 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -2029,28 +2131,28 @@
         <v>KL1001</v>
       </c>
       <c r="C3" t="str">
-        <v>スイングインパクト</v>
+        <v>2"</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>0.9g</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>2"</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>620</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -2074,7 +2176,7 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2082,31 +2184,31 @@
         <v>KLD10002</v>
       </c>
       <c r="B4" t="str">
-        <v>KL1002</v>
+        <v>KL1001</v>
       </c>
       <c r="C4" t="str">
-        <v>スイングインパクトファット</v>
+        <v>2.5"</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>1.3g</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>2.5"</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>620</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -2130,7 +2232,7 @@
         <v/>
       </c>
       <c r="R4" t="str">
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2138,31 +2240,31 @@
         <v>KLD10003</v>
       </c>
       <c r="B5" t="str">
-        <v>KL1003</v>
+        <v>KL1001</v>
       </c>
       <c r="C5" t="str">
-        <v>イージーシャイナー</v>
+        <v>3"</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>2.0g</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>3"</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>620</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -2186,7 +2288,7 @@
         <v/>
       </c>
       <c r="R5" t="str">
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2194,31 +2296,31 @@
         <v>KLD10004</v>
       </c>
       <c r="B6" t="str">
-        <v>KL1004</v>
+        <v>KL1001</v>
       </c>
       <c r="C6" t="str">
-        <v>グライドカマロン3.5"</v>
+        <v>3.5"</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>3.2g</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>3.5"</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -2242,7 +2344,7 @@
         <v/>
       </c>
       <c r="R6" t="str">
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2250,31 +2352,31 @@
         <v>KLD10005</v>
       </c>
       <c r="B7" t="str">
-        <v>KL1005</v>
+        <v>KL1001</v>
       </c>
       <c r="C7" t="str">
-        <v>フラッパーグラブ4"</v>
+        <v>4"</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>4.6g</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>4"</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -2298,7 +2400,7 @@
         <v/>
       </c>
       <c r="R7" t="str">
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2306,31 +2408,31 @@
         <v>KLD10006</v>
       </c>
       <c r="B8" t="str">
-        <v>KL1006</v>
+        <v>KL1001</v>
       </c>
       <c r="C8" t="str">
-        <v>ハイパースパイダー</v>
+        <v>4.5"</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>9.0g</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>4.5"</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -2354,7 +2456,7 @@
         <v/>
       </c>
       <c r="R8" t="str">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2362,31 +2464,31 @@
         <v>KLD10007</v>
       </c>
       <c r="B9" t="str">
-        <v>KL1007</v>
+        <v>KL1002</v>
       </c>
       <c r="C9" t="str">
-        <v>パドリンビーバー</v>
+        <v>2.8"</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>3.5g</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2.8"</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -2410,7 +2512,7 @@
         <v/>
       </c>
       <c r="R9" t="str">
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2418,31 +2520,31 @@
         <v>KLD10008</v>
       </c>
       <c r="B10" t="str">
-        <v>KL1008</v>
+        <v>KL1002</v>
       </c>
       <c r="C10" t="str">
-        <v>ネコカマロン</v>
+        <v>3.3"</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>5.6g</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>3.3"</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -2466,7 +2568,7 @@
         <v/>
       </c>
       <c r="R10" t="str">
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2474,31 +2576,31 @@
         <v>KLD10009</v>
       </c>
       <c r="B11" t="str">
-        <v>KL1009</v>
+        <v>KL1002</v>
       </c>
       <c r="C11" t="str">
-        <v>フレックスチャンク</v>
+        <v>3.8"</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>8.5g</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>3.8"</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -2522,7 +2624,7 @@
         <v/>
       </c>
       <c r="R11" t="str">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2530,31 +2632,31 @@
         <v>KLD10010</v>
       </c>
       <c r="B12" t="str">
-        <v>KL1010</v>
+        <v>KL1002</v>
       </c>
       <c r="C12" t="str">
-        <v>Easy Shaker</v>
+        <v>4.3"</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>10.3g</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>4.3"</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>860</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -2578,7 +2680,7 @@
         <v/>
       </c>
       <c r="R12" t="str">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -2586,31 +2688,31 @@
         <v>KLD10011</v>
       </c>
       <c r="B13" t="str">
-        <v>KL1011</v>
+        <v>KL1002</v>
       </c>
       <c r="C13" t="str">
-        <v>カスタムリーチ</v>
+        <v>4.8"</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>12.8g</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>4.8"</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>860</v>
       </c>
       <c r="I13" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -2634,7 +2736,7 @@
         <v/>
       </c>
       <c r="R13" t="str">
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2642,31 +2744,31 @@
         <v>KLD10012</v>
       </c>
       <c r="B14" t="str">
-        <v>KL1012</v>
+        <v>KL1002</v>
       </c>
       <c r="C14" t="str">
-        <v>ノイジーフラッパー</v>
+        <v>5.8"</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>22.8g</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>5.8"</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>860</v>
       </c>
       <c r="I14" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -2690,7 +2792,7 @@
         <v/>
       </c>
       <c r="R14" t="str">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -2698,31 +2800,31 @@
         <v>KLD10013</v>
       </c>
       <c r="B15" t="str">
-        <v>KL1013</v>
+        <v>KL1002</v>
       </c>
       <c r="C15" t="str">
-        <v>クレイジーフラッパー</v>
+        <v>6.8"</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>36.5g</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>6.8"</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>1080</v>
       </c>
       <c r="I15" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -2746,7 +2848,7 @@
         <v/>
       </c>
       <c r="R15" t="str">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -2754,31 +2856,31 @@
         <v>KLD10014</v>
       </c>
       <c r="B16" t="str">
-        <v>KL1014</v>
+        <v>KL1002</v>
       </c>
       <c r="C16" t="str">
-        <v>セクシーインパクト</v>
+        <v>7.8"</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>54.2g</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>7.8"</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>1080</v>
       </c>
       <c r="I16" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -2802,7 +2904,7 @@
         <v/>
       </c>
       <c r="R16" t="str">
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2810,31 +2912,31 @@
         <v>KLD10015</v>
       </c>
       <c r="B17" t="str">
-        <v>KL1015</v>
+        <v>KL1003</v>
       </c>
       <c r="C17" t="str">
-        <v>リトルスパイダー</v>
+        <v>2"</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>1.0 g</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>2"</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I17" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -2858,7 +2960,7 @@
         <v/>
       </c>
       <c r="R17" t="str">
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2866,31 +2968,31 @@
         <v>KLD10016</v>
       </c>
       <c r="B18" t="str">
-        <v>KL1016</v>
+        <v>KL1003</v>
       </c>
       <c r="C18" t="str">
-        <v>シャッドインパクト</v>
+        <v>3"</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>2.2 g</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>3"</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I18" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -2914,7 +3016,7 @@
         <v/>
       </c>
       <c r="R18" t="str">
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2922,31 +3024,31 @@
         <v>KLD10017</v>
       </c>
       <c r="B19" t="str">
-        <v>KL1017</v>
+        <v>KL1003</v>
       </c>
       <c r="C19" t="str">
-        <v>ソルティ・コアチューブ</v>
+        <v>3.5"</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>3.9 g</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>3.5"</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I19" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -2970,7 +3072,7 @@
         <v/>
       </c>
       <c r="R19" t="str">
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2978,31 +3080,31 @@
         <v>KLD10018</v>
       </c>
       <c r="B20" t="str">
-        <v>KL1018</v>
+        <v>KL1003</v>
       </c>
       <c r="C20" t="str">
-        <v>マッドワグ</v>
+        <v>4"</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>5.5 g</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>4"</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I20" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -3026,7 +3128,7 @@
         <v/>
       </c>
       <c r="R20" t="str">
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -3034,60 +3136,2860 @@
         <v>KLD10019</v>
       </c>
       <c r="B21" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="C21" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="D21" t="str">
+        <v>7.4 g</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>740</v>
+      </c>
+      <c r="I21" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="J21" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>KLD10020</v>
+      </c>
+      <c r="B22" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="C22" t="str">
+        <v>5"</v>
+      </c>
+      <c r="D22" t="str">
+        <v>10.4 g</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>5"</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>840</v>
+      </c>
+      <c r="I22" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="J22" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>KLD10021</v>
+      </c>
+      <c r="B23" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="C23" t="str">
+        <v>8"</v>
+      </c>
+      <c r="D23" t="str">
+        <v>43 g</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>8"</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>1080</v>
+      </c>
+      <c r="I23" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="J23" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>KLD10022</v>
+      </c>
+      <c r="B24" t="str">
+        <v>KL1004</v>
+      </c>
+      <c r="C24" t="str">
+        <v>グライドカマロン3.5"</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>2026-04-10T05:39:33.792Z</v>
+      </c>
+      <c r="J24" t="str">
+        <v>2026-04-10T05:39:33.792Z</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>KLD10023</v>
+      </c>
+      <c r="B25" t="str">
+        <v>KL1005</v>
+      </c>
+      <c r="C25" t="str">
+        <v>4"</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>4"</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>2026-04-10T05:39:35.679Z</v>
+      </c>
+      <c r="J25" t="str">
+        <v>2026-04-10T05:39:35.679Z</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>KLD10024</v>
+      </c>
+      <c r="B26" t="str">
+        <v>KL1006</v>
+      </c>
+      <c r="C26" t="str">
+        <v>3.2"</v>
+      </c>
+      <c r="D26" t="str">
+        <v>約5g</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>3.2"</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>2026-04-10T05:39:37.181Z</v>
+      </c>
+      <c r="J26" t="str">
+        <v>2026-04-10T05:39:37.181Z</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>KLD10025</v>
+      </c>
+      <c r="B27" t="str">
+        <v>KL1007</v>
+      </c>
+      <c r="C27" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>2026-04-10T05:39:39.295Z</v>
+      </c>
+      <c r="J27" t="str">
+        <v>2026-04-10T05:39:39.295Z</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>KLD10026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>KL1008</v>
+      </c>
+      <c r="C28" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="D28" t="str">
+        <v>約7.4g</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>2026-04-10T05:39:40.991Z</v>
+      </c>
+      <c r="J28" t="str">
+        <v>2026-04-10T05:39:40.991Z</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>KLD10027</v>
+      </c>
+      <c r="B29" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Small</v>
+      </c>
+      <c r="D29" t="str">
+        <v>約1.7g</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>Small</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>620</v>
+      </c>
+      <c r="I29" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J29" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>KLD10028</v>
+      </c>
+      <c r="B30" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Small-Medium</v>
+      </c>
+      <c r="D30" t="str">
+        <v>約3.3g</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>Small-Medium</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>620</v>
+      </c>
+      <c r="I30" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J30" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>KLD10029</v>
+      </c>
+      <c r="B31" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D31" t="str">
+        <v>6.5g</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>620</v>
+      </c>
+      <c r="I31" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J31" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>KLD10030</v>
+      </c>
+      <c r="B32" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Medium-Large</v>
+      </c>
+      <c r="D32" t="str">
+        <v>約8.4g</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>Medium-Large</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>670</v>
+      </c>
+      <c r="I32" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J32" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>KLD10031</v>
+      </c>
+      <c r="B33" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Large</v>
+      </c>
+      <c r="D33" t="str">
+        <v>約13.5g</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>Large</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>740</v>
+      </c>
+      <c r="I33" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J33" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>KLD10032</v>
+      </c>
+      <c r="B34" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D34" t="str">
+        <v>約0.5g</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>620</v>
+      </c>
+      <c r="I34" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J34" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>KLD10033</v>
+      </c>
+      <c r="B35" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="D35" t="str">
+        <v>約0.7g</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>620</v>
+      </c>
+      <c r="I35" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J35" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+      <c r="R35" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>KLD10034</v>
+      </c>
+      <c r="B36" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C36" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D36" t="str">
+        <v>約1.2g</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>620</v>
+      </c>
+      <c r="I36" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J36" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>KLD10035</v>
+      </c>
+      <c r="B37" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C37" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D37" t="str">
+        <v>約1.9g</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>620</v>
+      </c>
+      <c r="I37" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J37" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>KLD10036</v>
+      </c>
+      <c r="B38" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C38" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="D38" t="str">
+        <v>約3.3g</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>620</v>
+      </c>
+      <c r="I38" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J38" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>KLD10037</v>
+      </c>
+      <c r="B39" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C39" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="D39" t="str">
+        <v>約5.6g</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>740</v>
+      </c>
+      <c r="I39" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J39" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>KLD10038</v>
+      </c>
+      <c r="B40" t="str">
+        <v>KL1011</v>
+      </c>
+      <c r="C40" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D40" t="str">
+        <v>約1.3g</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>740</v>
+      </c>
+      <c r="I40" t="str">
+        <v>2026-04-10T05:39:48.055Z</v>
+      </c>
+      <c r="J40" t="str">
+        <v>2026-04-10T05:39:48.055Z</v>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>KLD10039</v>
+      </c>
+      <c r="B41" t="str">
+        <v>KL1012</v>
+      </c>
+      <c r="C41" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D41" t="str">
+        <v>16.3g</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>2026-04-10T05:39:51.253Z</v>
+      </c>
+      <c r="J41" t="str">
+        <v>2026-04-10T05:39:51.253Z</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>KLD10040</v>
+      </c>
+      <c r="B42" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C42" t="str">
+        <v>2.4および2.8インチ インナートレー×2※2.4"のみインナートレーを1枚増やし</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>2.4および2.8インチ インナートレー×2※2.4"のみインナートレーを1枚増やし</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J42" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>KLD10041</v>
+      </c>
+      <c r="B43" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C43" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D43" t="str">
+        <v>約1.2g</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>720</v>
+      </c>
+      <c r="I43" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J43" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>KLD10042</v>
+      </c>
+      <c r="B44" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C44" t="str">
+        <v>2.4"</v>
+      </c>
+      <c r="D44" t="str">
+        <v>約2.1g</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>2.4"</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>770</v>
+      </c>
+      <c r="I44" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J44" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>KLD10043</v>
+      </c>
+      <c r="B45" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C45" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="D45" t="str">
+        <v>3.4g</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>770</v>
+      </c>
+      <c r="I45" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J45" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>KLD10044</v>
+      </c>
+      <c r="B46" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C46" t="str">
+        <v>3.6"</v>
+      </c>
+      <c r="D46" t="str">
+        <v>6.6g</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>3.6"</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>820</v>
+      </c>
+      <c r="I46" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J46" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>KLD10045</v>
+      </c>
+      <c r="B47" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C47" t="str">
+        <v>4.4"</v>
+      </c>
+      <c r="D47" t="str">
+        <v>12.0g</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>4.4"</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>860</v>
+      </c>
+      <c r="I47" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J47" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>KLD10046</v>
+      </c>
+      <c r="B48" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C48" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="D48" t="str">
+        <v>1.5g</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>740</v>
+      </c>
+      <c r="I48" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J48" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>KLD10047</v>
+      </c>
+      <c r="B49" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C49" t="str">
+        <v>3.8"</v>
+      </c>
+      <c r="D49" t="str">
+        <v>3.3g</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>3.8"</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>740</v>
+      </c>
+      <c r="I49" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J49" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>KLD10048</v>
+      </c>
+      <c r="B50" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C50" t="str">
+        <v>4.8"</v>
+      </c>
+      <c r="D50" t="str">
+        <v>6.3g</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>4.8"</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>740</v>
+      </c>
+      <c r="I50" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J50" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>KLD10049</v>
+      </c>
+      <c r="B51" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C51" t="str">
+        <v>5.8"</v>
+      </c>
+      <c r="D51" t="str">
+        <v>10.6g</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>5.8"</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>860</v>
+      </c>
+      <c r="I51" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J51" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>KLD10050</v>
+      </c>
+      <c r="B52" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="C52" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D52" t="str">
+        <v>1.1g</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>740</v>
+      </c>
+      <c r="I52" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="J52" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>KLD10051</v>
+      </c>
+      <c r="B53" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="C53" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D53" t="str">
+        <v>1.7g</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>740</v>
+      </c>
+      <c r="I53" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="J53" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>KLD10052</v>
+      </c>
+      <c r="B54" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="C54" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2.7g</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>740</v>
+      </c>
+      <c r="I54" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="J54" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>KLD10053</v>
+      </c>
+      <c r="B55" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C55" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D55" t="str">
+        <v>0.9g</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>740</v>
+      </c>
+      <c r="I55" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J55" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>KLD10054</v>
+      </c>
+      <c r="B56" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C56" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2.2g</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>740</v>
+      </c>
+      <c r="I56" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J56" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>KLD10055</v>
+      </c>
+      <c r="B57" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C57" t="str">
+        <v>4"</v>
+      </c>
+      <c r="D57" t="str">
+        <v>5.2g</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>4"</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>740</v>
+      </c>
+      <c r="I57" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J57" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>KLD10056</v>
+      </c>
+      <c r="B58" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C58" t="str">
+        <v>5"</v>
+      </c>
+      <c r="D58" t="str">
+        <v>7.2g</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>5"</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>740</v>
+      </c>
+      <c r="I58" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J58" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>KLD10057</v>
+      </c>
+      <c r="B59" t="str">
+        <v>KL1017</v>
+      </c>
+      <c r="C59" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D59" t="str">
+        <v>7.8g</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>820</v>
+      </c>
+      <c r="I59" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="J59" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>KLD10058</v>
+      </c>
+      <c r="B60" t="str">
+        <v>KL1017</v>
+      </c>
+      <c r="C60" t="str">
+        <v>4.25"</v>
+      </c>
+      <c r="D60" t="str">
+        <v>14.0g</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>4.25"</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>960</v>
+      </c>
+      <c r="I60" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="J60" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>KLD10059</v>
+      </c>
+      <c r="B61" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Mini 2.5"</v>
+      </c>
+      <c r="D61" t="str">
+        <v>0.6g</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>Mini 2.5"</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>620</v>
+      </c>
+      <c r="I61" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J61" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>KLD10060</v>
+      </c>
+      <c r="B62" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Mini 3.5"</v>
+      </c>
+      <c r="D62" t="str">
+        <v>1.8g</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>Mini 3.5"</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>620</v>
+      </c>
+      <c r="I62" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J62" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>KLD10061</v>
+      </c>
+      <c r="B63" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Slim 4.5"</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2.9g</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>Slim 4.5"</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>620</v>
+      </c>
+      <c r="I63" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J63" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>KLD10062</v>
+      </c>
+      <c r="B64" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Original 7"</v>
+      </c>
+      <c r="D64" t="str">
+        <v>12.3g</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>Original 7"</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>740</v>
+      </c>
+      <c r="I64" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J64" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>KLD10063</v>
+      </c>
+      <c r="B65" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Long 8"</v>
+      </c>
+      <c r="D65" t="str">
+        <v>7.7g</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>Long 8"</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>740</v>
+      </c>
+      <c r="I65" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J65" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>KLD10064</v>
+      </c>
+      <c r="B66" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Long 11"</v>
+      </c>
+      <c r="D66" t="str">
+        <v>10.9g</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>Long 11"</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>740</v>
+      </c>
+      <c r="I66" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J66" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>KLD10065</v>
+      </c>
+      <c r="B67" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C67" t="str">
+        <v>ジグヘッドリグ 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>ジグヘッドリグ 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J67" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>KLD10066</v>
+      </c>
+      <c r="B68" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C68" t="str">
+        <v>スモラバトレーラー 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>スモラバトレーラー 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J68" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>KLD10067</v>
+      </c>
+      <c r="B69" t="str">
         <v>KL1019</v>
       </c>
-      <c r="C21" t="str">
-        <v>ライブインパクト</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v/>
-      </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
-      </c>
-      <c r="J21" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
-      </c>
-      <c r="R21" t="str">
-        <v/>
+      <c r="C69" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="J69" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>KLD10068</v>
+      </c>
+      <c r="B70" t="str">
+        <v>KL1019</v>
+      </c>
+      <c r="C70" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="J70" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>KLD10069</v>
+      </c>
+      <c r="B71" t="str">
+        <v>KL1019</v>
+      </c>
+      <c r="C71" t="str">
+        <v>4"</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>4"</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="J71" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R71"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3151,7 +6053,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KLD10020</v>
+        <v>KLD10070</v>
       </c>
       <c r="B2" t="str">
         <v>KL1020</v>
@@ -3175,10 +6077,10 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-10T05:01:36.834Z</v>
+        <v>2026-04-10T05:40:37.872Z</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -3204,22 +6106,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KLD10021</v>
+        <v>KLD10071</v>
       </c>
       <c r="B3" t="str">
         <v>KL1021</v>
       </c>
       <c r="C3" t="str">
-        <v>ベイビーTEE-BONE スピナーベイト</v>
+        <v>ウエイトは3サイズで展開</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>1/2oz</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>ウエイトは3サイズで展開</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -3228,10 +6130,10 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-10T05:01:39.158Z</v>
+        <v>2026-04-10T05:40:41.227Z</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -3257,7 +6159,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KLD10022</v>
+        <v>KLD10072</v>
       </c>
       <c r="B4" t="str">
         <v>KL1022</v>
@@ -3281,10 +6183,10 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-10T05:01:40.855Z</v>
+        <v>2026-04-10T05:40:43.082Z</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -3374,22 +6276,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KLD10023</v>
+        <v>KLD10073</v>
       </c>
       <c r="B2" t="str">
         <v>KL1023</v>
       </c>
       <c r="C2" t="str">
-        <v>ランブレードジグ</v>
+        <v>ウエイトは3サイズウエイトラインナップは3/8、1/2、5/8oz の3サイズをご用意しております</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>5/8oz</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>ウエイトは3サイズウエイトラインナップは3/8、1/2、5/8oz の3サイズをご用意しております</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -3398,10 +6300,10 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-10T05:01:42.781Z</v>
+        <v>2026-04-10T05:40:45.753Z</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -3427,7 +6329,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KLD10024</v>
+        <v>KLD10074</v>
       </c>
       <c r="B3" t="str">
         <v>KL1024</v>
@@ -3451,10 +6353,10 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-10T05:01:44.227Z</v>
+        <v>2026-04-10T05:40:47.419Z</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -3480,7 +6382,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KLD10025</v>
+        <v>KLD10075</v>
       </c>
       <c r="B4" t="str">
         <v>KL1025</v>
@@ -3504,10 +6406,10 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-10T05:01:45.770Z</v>
+        <v>2026-04-10T05:40:50.108Z</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -3533,7 +6435,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KLD10026</v>
+        <v>KLD10076</v>
       </c>
       <c r="B5" t="str">
         <v>KL1026</v>
@@ -3557,10 +6459,10 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-10T05:01:47.045Z</v>
+        <v>2026-04-10T05:40:51.763Z</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -3586,7 +6488,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>KLD10027</v>
+        <v>KLD10077</v>
       </c>
       <c r="B6" t="str">
         <v>KL1027</v>
@@ -3610,10 +6512,10 @@
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-10T05:01:48.745Z</v>
+        <v>2026-04-10T05:40:53.441Z</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -3639,22 +6541,22 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>KLD10028</v>
+        <v>KLD10078</v>
       </c>
       <c r="B7" t="str">
         <v>KL1028</v>
       </c>
       <c r="C7" t="str">
-        <v>ラバージグ モデル Ⅳ ヘビーデューティージグ</v>
+        <v>パワーゲームに必要な3サイズ</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>1oz</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>パワーゲームに必要な3サイズ</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -3663,10 +6565,10 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-10T05:01:50.828Z</v>
+        <v>2026-04-10T05:40:55.491Z</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -3692,7 +6594,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>KLD10029</v>
+        <v>KLD10079</v>
       </c>
       <c r="B8" t="str">
         <v>KL1029</v>
@@ -3716,10 +6618,10 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-10T05:01:52.477Z</v>
+        <v>2026-04-10T05:40:57.481Z</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -3745,7 +6647,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>KLD10030</v>
+        <v>KLD10080</v>
       </c>
       <c r="B9" t="str">
         <v>KL1030</v>
@@ -3769,10 +6671,10 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-10T05:01:55.893Z</v>
+        <v>2026-04-10T05:41:00.188Z</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -3798,7 +6700,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>KLD10031</v>
+        <v>KLD10081</v>
       </c>
       <c r="B10" t="str">
         <v>KL1031</v>
@@ -3822,10 +6724,10 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-10T05:01:57.179Z</v>
+        <v>2026-04-10T05:41:01.840Z</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -3851,7 +6753,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>KLD10032</v>
+        <v>KLD10082</v>
       </c>
       <c r="B11" t="str">
         <v>KL1032</v>
@@ -3875,10 +6777,10 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-10T05:01:58.540Z</v>
+        <v>2026-04-10T05:41:03.332Z</v>
       </c>
       <c r="K11" t="str">
         <v/>

--- a/GearSage-client/pkgGear/data_raw/keitech_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/keitech_lure_import.xlsx
@@ -481,7 +481,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K2" t="str">
-        <v>pkgGear/images/lure/KEITECH/202501241430404411.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202501241430404411.jpg</v>
       </c>
       <c r="L2" t="str">
         <v>2026-04-10T05:39:11.615Z</v>
@@ -528,7 +528,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K3" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191540483278.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191540483278.jpg</v>
       </c>
       <c r="L3" t="str">
         <v>2026-04-10T05:39:18.540Z</v>
@@ -575,7 +575,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K4" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191547352876.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191547352876.jpg</v>
       </c>
       <c r="L4" t="str">
         <v>2026-04-10T05:39:27.448Z</v>
@@ -622,7 +622,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K5" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191558078979.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191558078979.jpg</v>
       </c>
       <c r="L5" t="str">
         <v>2026-04-10T05:39:32.312Z</v>
@@ -669,7 +669,7 @@
         <v>variable</v>
       </c>
       <c r="K6" t="str">
-        <v>pkgGear/images/lure/KEITECH/202401161646502833.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202401161646502833.jpg</v>
       </c>
       <c r="L6" t="str">
         <v>2026-04-10T05:39:33.792Z</v>
@@ -716,7 +716,7 @@
         <v>variable</v>
       </c>
       <c r="K7" t="str">
-        <v>pkgGear/images/lure/KEITECH/202401161654221750.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202401161654221750.jpg</v>
       </c>
       <c r="L7" t="str">
         <v>2026-04-10T05:39:35.679Z</v>
@@ -763,7 +763,7 @@
         <v>variable</v>
       </c>
       <c r="K8" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191655435515.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191655435515.jpg</v>
       </c>
       <c r="L8" t="str">
         <v>2026-04-10T05:39:37.181Z</v>
@@ -810,7 +810,7 @@
         <v>variable</v>
       </c>
       <c r="K9" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191701313136.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191701313136.jpg</v>
       </c>
       <c r="L9" t="str">
         <v>2026-04-10T05:39:39.295Z</v>
@@ -857,7 +857,7 @@
         <v>variable</v>
       </c>
       <c r="K10" t="str">
-        <v>pkgGear/images/lure/KEITECH/20250418163325698.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/20250418163325698.jpg</v>
       </c>
       <c r="L10" t="str">
         <v>2026-04-10T05:39:40.991Z</v>
@@ -904,7 +904,7 @@
         <v>variable</v>
       </c>
       <c r="K11" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191729594683.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191729594683.jpg</v>
       </c>
       <c r="L11" t="str">
         <v>2026-04-10T05:39:42.698Z</v>
@@ -951,7 +951,7 @@
         <v>variable</v>
       </c>
       <c r="K12" t="str">
-        <v>pkgGear/images/lure/KEITECH/202208011701561170.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202208011701561170.jpg</v>
       </c>
       <c r="L12" t="str">
         <v>2026-04-10T05:39:45.196Z</v>
@@ -998,7 +998,7 @@
         <v>variable</v>
       </c>
       <c r="K13" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191804546996.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191804546996.jpg</v>
       </c>
       <c r="L13" t="str">
         <v>2026-04-10T05:39:48.055Z</v>
@@ -1045,7 +1045,7 @@
         <v>variable</v>
       </c>
       <c r="K14" t="str">
-        <v>pkgGear/images/lure/KEITECH/202208011702381439.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202208011702381439.jpg</v>
       </c>
       <c r="L14" t="str">
         <v>2026-04-10T05:39:51.253Z</v>
@@ -1092,7 +1092,7 @@
         <v>variable</v>
       </c>
       <c r="K15" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191814411193.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191814411193.jpg</v>
       </c>
       <c r="L15" t="str">
         <v>2026-04-10T05:39:55.263Z</v>
@@ -1139,7 +1139,7 @@
         <v>variable</v>
       </c>
       <c r="K16" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191820097952.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191820097952.jpg</v>
       </c>
       <c r="L16" t="str">
         <v>2026-04-10T05:40:06.614Z</v>
@@ -1186,7 +1186,7 @@
         <v>variable</v>
       </c>
       <c r="K17" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191828058722.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191828058722.jpg</v>
       </c>
       <c r="L17" t="str">
         <v>2026-04-10T05:40:13.153Z</v>
@@ -1233,7 +1233,7 @@
         <v>variable</v>
       </c>
       <c r="K18" t="str">
-        <v>pkgGear/images/lure/KEITECH/20221219183446307.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/20221219183446307.jpg</v>
       </c>
       <c r="L18" t="str">
         <v>2026-04-10T05:40:20.195Z</v>
@@ -1280,7 +1280,7 @@
         <v>variable</v>
       </c>
       <c r="K19" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191843366790.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191843366790.jpg</v>
       </c>
       <c r="L19" t="str">
         <v>2026-04-10T05:40:24.698Z</v>
@@ -1327,7 +1327,7 @@
         <v>variable</v>
       </c>
       <c r="K20" t="str">
-        <v>pkgGear/images/lure/KEITECH/20221219174541338.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/20221219174541338.jpg</v>
       </c>
       <c r="L20" t="str">
         <v>2026-04-10T05:40:28.288Z</v>
@@ -1374,7 +1374,7 @@
         <v>variable</v>
       </c>
       <c r="K21" t="str">
-        <v>pkgGear/images/lure/KEITECH/202212191850068911.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202212191850068911.jpg</v>
       </c>
       <c r="L21" t="str">
         <v>2026-04-10T05:40:33.878Z</v>
@@ -1421,7 +1421,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K22" t="str">
-        <v>pkgGear/images/lure/KEITECH/20260128162612996.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/20260128162612996.jpg</v>
       </c>
       <c r="L22" t="str">
         <v>2026-04-10T05:40:37.872Z</v>
@@ -1468,7 +1468,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K23" t="str">
-        <v>pkgGear/images/lure/KEITECH/202501241436271305.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202501241436271305.jpg</v>
       </c>
       <c r="L23" t="str">
         <v>2026-04-10T05:40:41.227Z</v>
@@ -1515,7 +1515,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K24" t="str">
-        <v>pkgGear/images/lure/KEITECH/202403141759512800.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202403141759512800.jpg</v>
       </c>
       <c r="L24" t="str">
         <v>2026-04-10T05:40:43.082Z</v>
@@ -1562,7 +1562,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K25" t="str">
-        <v>pkgGear/images/lure/KEITECH/202407031757493567.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202407031757493567.jpg</v>
       </c>
       <c r="L25" t="str">
         <v>2026-04-10T05:40:45.753Z</v>
@@ -1609,7 +1609,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K26" t="str">
-        <v>pkgGear/images/lure/KEITECH/202208011732559977.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202208011732559977.jpg</v>
       </c>
       <c r="L26" t="str">
         <v>2026-04-10T05:40:47.419Z</v>
@@ -1656,7 +1656,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K27" t="str">
-        <v>pkgGear/images/lure/KEITECH/202601091020542528.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202601091020542528.jpg</v>
       </c>
       <c r="L27" t="str">
         <v>2026-04-10T05:40:50.108Z</v>
@@ -1703,7 +1703,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K28" t="str">
-        <v>pkgGear/images/lure/KEITECH/202208011733324565.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202208011733324565.jpg</v>
       </c>
       <c r="L28" t="str">
         <v>2026-04-10T05:40:51.763Z</v>
@@ -1750,7 +1750,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K29" t="str">
-        <v>pkgGear/images/lure/KEITECH/202401161640403055.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202401161640403055.jpg</v>
       </c>
       <c r="L29" t="str">
         <v>2026-04-10T05:40:53.441Z</v>
@@ -1797,7 +1797,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K30" t="str">
-        <v>pkgGear/images/lure/KEITECH/202401161641262646.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202401161641262646.jpg</v>
       </c>
       <c r="L30" t="str">
         <v>2026-04-10T05:40:55.491Z</v>
@@ -1844,7 +1844,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K31" t="str">
-        <v>pkgGear/images/lure/KEITECH/202501300927538741.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202501300927538741.jpg</v>
       </c>
       <c r="L31" t="str">
         <v>2026-04-10T05:40:57.481Z</v>
@@ -1891,7 +1891,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K32" t="str">
-        <v>pkgGear/images/lure/KEITECH/202209221617177492.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202209221617177492.jpg</v>
       </c>
       <c r="L32" t="str">
         <v>2026-04-10T05:41:00.188Z</v>
@@ -1938,7 +1938,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K33" t="str">
-        <v>pkgGear/images/lure/KEITECH/202208011735477115.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202208011735477115.jpg</v>
       </c>
       <c r="L33" t="str">
         <v>2026-04-10T05:41:01.840Z</v>
@@ -1985,7 +1985,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K34" t="str">
-        <v>pkgGear/images/lure/KEITECH/202208011736112779.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/KEITECH_lures/202208011736112779.jpg</v>
       </c>
       <c r="L34" t="str">
         <v>2026-04-10T05:41:03.332Z</v>
